--- a/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 13,44</t>
+          <t>-1,2; 13,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 8,89</t>
+          <t>-6,51; 9,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 14,3</t>
+          <t>-2,06; 12,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 8,14</t>
+          <t>-3,09; 8,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 33,06</t>
+          <t>-2,43; 33,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 18,93</t>
+          <t>-12,17; 21,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 35,4</t>
+          <t>-4,11; 30,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 27,99</t>
+          <t>-9,25; 28,49</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 15,25</t>
+          <t>0,96; 15,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 17,94</t>
+          <t>1,64; 16,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 9,96</t>
+          <t>-5,4; 9,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 3,61</t>
+          <t>-8,62; 3,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 38,54</t>
+          <t>2,03; 38,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 37,33</t>
+          <t>3,06; 33,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 22,53</t>
+          <t>-10,05; 22,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 11,74</t>
+          <t>-24,32; 12,27</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 18,85</t>
+          <t>2,68; 19,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 19,45</t>
+          <t>4,93; 19,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 19,51</t>
+          <t>2,48; 19,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 40,1</t>
+          <t>10,58; 41,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 43,79</t>
+          <t>5,51; 45,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 36,36</t>
+          <t>8,33; 35,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 37,0</t>
+          <t>4,53; 37,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,46; 473,68</t>
+          <t>30,83; 495,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 15,2</t>
+          <t>6,37; 15,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,72</t>
+          <t>1,17; 10,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 5,74</t>
+          <t>-3,98; 5,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 37,39</t>
+          <t>-1,47; 35,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 32,82</t>
+          <t>12,51; 33,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 19,54</t>
+          <t>2,11; 19,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 11,24</t>
+          <t>-7,32; 11,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 106,45</t>
+          <t>-4,02; 101,3</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 19,55</t>
+          <t>4,78; 19,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,51; 22,88</t>
+          <t>11,06; 22,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 22,46</t>
+          <t>11,77; 22,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 11,73</t>
+          <t>-5,93; 12,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,52; 44,44</t>
+          <t>8,95; 42,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 43,57</t>
+          <t>18,21; 42,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,93; 45,49</t>
+          <t>21,29; 45,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 32,69</t>
+          <t>-13,97; 35,77</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,2; 48,09</t>
+          <t>37,23; 48,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,36; 42,62</t>
+          <t>29,06; 42,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,58; 41,34</t>
+          <t>29,43; 41,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,91; 29,61</t>
+          <t>7,22; 28,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>128,1; 245,81</t>
+          <t>129,85; 247,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,82; 136,21</t>
+          <t>67,98; 134,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75,3; 151,63</t>
+          <t>79,47; 159,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,51; 190,38</t>
+          <t>20,69; 169,18</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,57; 18,23</t>
+          <t>13,77; 18,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,37; 16,11</t>
+          <t>11,35; 16,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 13,74</t>
+          <t>9,19; 13,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 23,67</t>
+          <t>5,55; 21,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,58; 42,44</t>
+          <t>30,21; 43,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,61; 30,72</t>
+          <t>20,65; 30,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,45; 28,6</t>
+          <t>17,96; 28,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,56; 89,35</t>
+          <t>16,08; 77,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 13,17</t>
+          <t>-1,4; 13,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 9,4</t>
+          <t>-6,86; 9,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 12,9</t>
+          <t>-1,73; 12,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 8,09</t>
+          <t>-3,19; 7,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 33,18</t>
+          <t>-3,13; 33,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 21,41</t>
+          <t>-13,12; 20,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 30,95</t>
+          <t>-3,15; 29,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 28,49</t>
+          <t>-8,92; 28,61</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-1,9</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,0%</t>
+          <t>-6,04%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 15,31</t>
+          <t>1,44; 15,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 16,58</t>
+          <t>2,13; 18,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 9,82</t>
+          <t>-5,5; 9,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 3,65</t>
+          <t>-7,7; 3,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 38,16</t>
+          <t>3,15; 39,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 33,85</t>
+          <t>3,81; 38,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 22,58</t>
+          <t>-10,54; 22,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 12,27</t>
+          <t>-21,88; 13,23</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,09</t>
+          <t>13,31</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>118,96%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 19,77</t>
+          <t>1,7; 19,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 19,45</t>
+          <t>5,9; 20,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 19,42</t>
+          <t>1,97; 19,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,58; 41,21</t>
+          <t>6,52; 20,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 45,73</t>
+          <t>3,57; 45,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 35,42</t>
+          <t>9,38; 36,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 37,08</t>
+          <t>3,49; 37,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,83; 495,34</t>
+          <t>18,91; 75,14</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 15,8</t>
+          <t>6,5; 15,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,72</t>
+          <t>1,42; 10,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 5,7</t>
+          <t>-3,88; 5,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 35,24</t>
+          <t>-3,8; 4,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,51; 33,6</t>
+          <t>12,86; 34,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 19,79</t>
+          <t>2,13; 19,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 11,04</t>
+          <t>-7,13; 9,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 101,3</t>
+          <t>-10,0; 13,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>12,3</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 19,15</t>
+          <t>4,68; 18,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,06; 22,48</t>
+          <t>10,99; 22,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 22,32</t>
+          <t>11,96; 22,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 12,74</t>
+          <t>6,42; 17,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 42,95</t>
+          <t>9,04; 41,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,21; 42,66</t>
+          <t>18,24; 42,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,29; 45,17</t>
+          <t>20,79; 45,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 35,77</t>
+          <t>16,99; 55,15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>22,04</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>100,27%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,23; 48,13</t>
+          <t>37,42; 47,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,06; 42,31</t>
+          <t>28,96; 41,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,43; 41,93</t>
+          <t>29,59; 42,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,22; 28,54</t>
+          <t>12,17; 29,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>129,85; 247,14</t>
+          <t>131,86; 248,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,98; 134,85</t>
+          <t>67,11; 132,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,47; 159,77</t>
+          <t>80,68; 160,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,69; 169,18</t>
+          <t>39,83; 204,65</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,29</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,77; 18,51</t>
+          <t>13,34; 18,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,35; 16,02</t>
+          <t>11,3; 16,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,19; 13,94</t>
+          <t>8,86; 13,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,55; 21,96</t>
+          <t>5,12; 9,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,21; 43,27</t>
+          <t>29,17; 42,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,65; 30,56</t>
+          <t>20,45; 30,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,96; 28,93</t>
+          <t>17,27; 28,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,08; 77,55</t>
+          <t>15,22; 30,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Población que convive con personas con enfermedades crónicas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
